--- a/engagement_survey_forms/011_nail_salon_social_media_engagement_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/011_nail_salon_social_media_engagement_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What platforms do you currently use?</t>
+          <t>Social Media Platforms</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Which platforms do you currently use?</t>
+          <t>Social Media Channels</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Which platforms do you currently use?</t>
+          <t>Preferred Platforms 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What platforms do you currently use?</t>
+          <t>Preferred Platforms 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>current_sns_2</t>
+          <t>current_sns_2_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What social media do you currently use?</t>
+          <t>Current Sns 2 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What social media do you currently use?</t>
+          <t>Current Channels 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Which platforms do you currently use?</t>
+          <t>Current Sns 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What social media do you currently use?</t>
+          <t>Current Channels 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Which platforms do you currently use?</t>
+          <t>Current Sns 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>current_sns_2_choices</t>
+          <t>current_sns_2_2_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
